--- a/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-09.xlsx
+++ b/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-09.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:58:32</t>
+          <t>2026-10-14 22:57:00</t>
         </is>
       </c>
     </row>

--- a/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-09.xlsx
+++ b/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-09.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:57:00</t>
+          <t>2026-10-15 02:05:10</t>
         </is>
       </c>
     </row>

--- a/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-09.xlsx
+++ b/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-09.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-15 02:05:10</t>
+          <t>2026-10-15 02:51:34</t>
         </is>
       </c>
     </row>
@@ -1751,14 +1751,10 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P4" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr"/>
       <c r="Q4" s="15" t="inlineStr">
         <is>
           <t>80313677</t>
@@ -1868,10 +1864,14 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="Q5" s="15" t="inlineStr">
         <is>
           <t>30769321</t>
@@ -1985,10 +1985,14 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>30769931-1</t>
@@ -2845,10 +2849,14 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>46981924</t>
@@ -3604,10 +3612,14 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P7" s="12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="Q7" s="15" t="inlineStr">
         <is>
           <t>30770213</t>
@@ -3717,10 +3729,14 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>SD-026</t>
@@ -4260,10 +4276,14 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>02434916</t>
@@ -5154,14 +5174,10 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr"/>
       <c r="Q7" s="15" t="inlineStr">
         <is>
           <t>30769343</t>
@@ -5271,14 +5287,10 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr"/>
       <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>12345678</t>
@@ -6725,6 +6737,50 @@
           "precio_m3": 4.0
         }
       ]
+    },
+    "B": {
+      "nombre": "Comercial",
+      "cargo_fijo": 2.5,
+      "tarifa_desague": 0.0,
+      "rangos": [
+        {
+          "m3_desde": 0,
+          "m3_hasta": 10,
+          "precio_m3": 1.5
+        },
+        {
+          "m3_desde": 10,
+          "m3_hasta": 20,
+          "precio_m3": 2.0
+        },
+        {
+          "m3_desde": 20,
+          "m3_hasta": null,
+          "precio_m3": 3.0
+        }
+      ]
+    },
+    "C": {
+      "nombre": "Estatal / Social",
+      "cargo_fijo": 1.5,
+      "tarifa_desague": 0.0,
+      "rangos": [
+        {
+          "m3_desde": 0,
+          "m3_hasta": 10,
+          "precio_m3": 1.0
+        },
+        {
+          "m3_desde": 10,
+          "m3_hasta": 20,
+          "precio_m3": 1.5
+        },
+        {
+          "m3_desde": 20,
+          "m3_hasta": null,
+          "precio_m3": 2.5
+        }
+      ]
     }
   },
   "lectores": {
